--- a/artfynd/A 35706-2023 artfynd.xlsx
+++ b/artfynd/A 35706-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113324581</v>
+        <v>113324582</v>
       </c>
       <c r="B2" t="n">
-        <v>78105</v>
+        <v>79184</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>383925</v>
+        <v>384098</v>
       </c>
       <c r="R2" t="n">
-        <v>6721620</v>
+        <v>6721548</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113324584</v>
+        <v>113324581</v>
       </c>
       <c r="B3" t="n">
-        <v>89993</v>
+        <v>78121</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384184</v>
+        <v>383925</v>
       </c>
       <c r="R3" t="n">
-        <v>6721713</v>
+        <v>6721620</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113324583</v>
+        <v>113324584</v>
       </c>
       <c r="B4" t="n">
-        <v>5164</v>
+        <v>90009</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384140</v>
+        <v>384184</v>
       </c>
       <c r="R4" t="n">
-        <v>6721585</v>
+        <v>6721713</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113324582</v>
+        <v>113324583</v>
       </c>
       <c r="B5" t="n">
-        <v>79168</v>
+        <v>5164</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384098</v>
+        <v>384140</v>
       </c>
       <c r="R5" t="n">
-        <v>6721548</v>
+        <v>6721585</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35706-2023 artfynd.xlsx
+++ b/artfynd/A 35706-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113324581</v>
+        <v>113324583</v>
       </c>
       <c r="B3" t="n">
-        <v>78121</v>
+        <v>5164</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>383925</v>
+        <v>384140</v>
       </c>
       <c r="R3" t="n">
-        <v>6721620</v>
+        <v>6721585</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113324583</v>
+        <v>113324581</v>
       </c>
       <c r="B5" t="n">
-        <v>5164</v>
+        <v>78121</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384140</v>
+        <v>383925</v>
       </c>
       <c r="R5" t="n">
-        <v>6721585</v>
+        <v>6721620</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35706-2023 artfynd.xlsx
+++ b/artfynd/A 35706-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113324582</v>
+        <v>113324584</v>
       </c>
       <c r="B2" t="n">
-        <v>79184</v>
+        <v>90021</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384098</v>
+        <v>384184</v>
       </c>
       <c r="R2" t="n">
-        <v>6721548</v>
+        <v>6721713</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113324584</v>
+        <v>113324582</v>
       </c>
       <c r="B4" t="n">
-        <v>90009</v>
+        <v>79196</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384184</v>
+        <v>384098</v>
       </c>
       <c r="R4" t="n">
-        <v>6721713</v>
+        <v>6721548</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>113324581</v>
       </c>
       <c r="B5" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 35706-2023 artfynd.xlsx
+++ b/artfynd/A 35706-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113324584</v>
+        <v>113324581</v>
       </c>
       <c r="B2" t="n">
-        <v>90021</v>
+        <v>78133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384184</v>
+        <v>383925</v>
       </c>
       <c r="R2" t="n">
-        <v>6721713</v>
+        <v>6721620</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113324583</v>
+        <v>113324582</v>
       </c>
       <c r="B3" t="n">
-        <v>5164</v>
+        <v>79196</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384140</v>
+        <v>384098</v>
       </c>
       <c r="R3" t="n">
-        <v>6721585</v>
+        <v>6721548</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113324582</v>
+        <v>113324583</v>
       </c>
       <c r="B4" t="n">
-        <v>79196</v>
+        <v>5164</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384098</v>
+        <v>384140</v>
       </c>
       <c r="R4" t="n">
-        <v>6721548</v>
+        <v>6721585</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113324581</v>
+        <v>113324584</v>
       </c>
       <c r="B5" t="n">
-        <v>78133</v>
+        <v>90021</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>383925</v>
+        <v>384184</v>
       </c>
       <c r="R5" t="n">
-        <v>6721620</v>
+        <v>6721713</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35706-2023 artfynd.xlsx
+++ b/artfynd/A 35706-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113324581</v>
+        <v>113324583</v>
       </c>
       <c r="B2" t="n">
-        <v>78133</v>
+        <v>5164</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>383925</v>
+        <v>384140</v>
       </c>
       <c r="R2" t="n">
-        <v>6721620</v>
+        <v>6721585</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
         <v>113324582</v>
       </c>
       <c r="B3" t="n">
-        <v>79196</v>
+        <v>79218</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113324583</v>
+        <v>113324581</v>
       </c>
       <c r="B4" t="n">
-        <v>5164</v>
+        <v>78155</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384140</v>
+        <v>383925</v>
       </c>
       <c r="R4" t="n">
-        <v>6721585</v>
+        <v>6721620</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>113324584</v>
       </c>
       <c r="B5" t="n">
-        <v>90021</v>
+        <v>90043</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 35706-2023 artfynd.xlsx
+++ b/artfynd/A 35706-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113324583</v>
+        <v>113324584</v>
       </c>
       <c r="B2" t="n">
-        <v>5164</v>
+        <v>90047</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384140</v>
+        <v>384184</v>
       </c>
       <c r="R2" t="n">
-        <v>6721585</v>
+        <v>6721713</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113324582</v>
+        <v>113324583</v>
       </c>
       <c r="B3" t="n">
-        <v>79218</v>
+        <v>5164</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384098</v>
+        <v>384140</v>
       </c>
       <c r="R3" t="n">
-        <v>6721548</v>
+        <v>6721585</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113324581</v>
+        <v>113324582</v>
       </c>
       <c r="B4" t="n">
-        <v>78155</v>
+        <v>79222</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>383925</v>
+        <v>384098</v>
       </c>
       <c r="R4" t="n">
-        <v>6721620</v>
+        <v>6721548</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113324584</v>
+        <v>113324581</v>
       </c>
       <c r="B5" t="n">
-        <v>90043</v>
+        <v>78158</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384184</v>
+        <v>383925</v>
       </c>
       <c r="R5" t="n">
-        <v>6721713</v>
+        <v>6721620</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35706-2023 artfynd.xlsx
+++ b/artfynd/A 35706-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113324584</v>
+        <v>113324583</v>
       </c>
       <c r="B2" t="n">
-        <v>90047</v>
+        <v>5164</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384184</v>
+        <v>384140</v>
       </c>
       <c r="R2" t="n">
-        <v>6721713</v>
+        <v>6721585</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113324583</v>
+        <v>113324584</v>
       </c>
       <c r="B3" t="n">
-        <v>5164</v>
+        <v>90047</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384140</v>
+        <v>384184</v>
       </c>
       <c r="R3" t="n">
-        <v>6721585</v>
+        <v>6721713</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113324582</v>
+        <v>113324581</v>
       </c>
       <c r="B4" t="n">
-        <v>79222</v>
+        <v>78158</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384098</v>
+        <v>383925</v>
       </c>
       <c r="R4" t="n">
-        <v>6721548</v>
+        <v>6721620</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113324581</v>
+        <v>113324582</v>
       </c>
       <c r="B5" t="n">
-        <v>78158</v>
+        <v>79222</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>383925</v>
+        <v>384098</v>
       </c>
       <c r="R5" t="n">
-        <v>6721620</v>
+        <v>6721548</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35706-2023 artfynd.xlsx
+++ b/artfynd/A 35706-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113324583</v>
+        <v>113324584</v>
       </c>
       <c r="B2" t="n">
-        <v>5164</v>
+        <v>90053</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384140</v>
+        <v>384184</v>
       </c>
       <c r="R2" t="n">
-        <v>6721585</v>
+        <v>6721713</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113324584</v>
+        <v>113324583</v>
       </c>
       <c r="B3" t="n">
-        <v>90047</v>
+        <v>5164</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384184</v>
+        <v>384140</v>
       </c>
       <c r="R3" t="n">
-        <v>6721713</v>
+        <v>6721585</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>113324581</v>
       </c>
       <c r="B4" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>113324582</v>
       </c>
       <c r="B5" t="n">
-        <v>79222</v>
+        <v>79228</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 35706-2023 artfynd.xlsx
+++ b/artfynd/A 35706-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113324584</v>
+        <v>113324581</v>
       </c>
       <c r="B2" t="n">
-        <v>90053</v>
+        <v>78164</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384184</v>
+        <v>383925</v>
       </c>
       <c r="R2" t="n">
-        <v>6721713</v>
+        <v>6721620</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113324581</v>
+        <v>113324582</v>
       </c>
       <c r="B4" t="n">
-        <v>78164</v>
+        <v>79228</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>383925</v>
+        <v>384098</v>
       </c>
       <c r="R4" t="n">
-        <v>6721620</v>
+        <v>6721548</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113324582</v>
+        <v>113324584</v>
       </c>
       <c r="B5" t="n">
-        <v>79228</v>
+        <v>90053</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384098</v>
+        <v>384184</v>
       </c>
       <c r="R5" t="n">
-        <v>6721548</v>
+        <v>6721713</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35706-2023 artfynd.xlsx
+++ b/artfynd/A 35706-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113324581</v>
+        <v>113324584</v>
       </c>
       <c r="B2" t="n">
-        <v>78164</v>
+        <v>90060</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>383925</v>
+        <v>384184</v>
       </c>
       <c r="R2" t="n">
-        <v>6721620</v>
+        <v>6721713</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>113324582</v>
       </c>
       <c r="B4" t="n">
-        <v>79228</v>
+        <v>79235</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113324584</v>
+        <v>113324581</v>
       </c>
       <c r="B5" t="n">
-        <v>90053</v>
+        <v>78171</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384184</v>
+        <v>383925</v>
       </c>
       <c r="R5" t="n">
-        <v>6721713</v>
+        <v>6721620</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35706-2023 artfynd.xlsx
+++ b/artfynd/A 35706-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113324584</v>
       </c>
       <c r="B2" t="n">
-        <v>90060</v>
+        <v>90063</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113324583</v>
+        <v>113324581</v>
       </c>
       <c r="B3" t="n">
-        <v>5164</v>
+        <v>78173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384140</v>
+        <v>383925</v>
       </c>
       <c r="R3" t="n">
-        <v>6721585</v>
+        <v>6721620</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>113324582</v>
       </c>
       <c r="B4" t="n">
-        <v>79235</v>
+        <v>79237</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113324581</v>
+        <v>113324583</v>
       </c>
       <c r="B5" t="n">
-        <v>78171</v>
+        <v>5164</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>383925</v>
+        <v>384140</v>
       </c>
       <c r="R5" t="n">
-        <v>6721620</v>
+        <v>6721585</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 35706-2023 artfynd.xlsx
+++ b/artfynd/A 35706-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35706-2023 artfynd.xlsx
+++ b/artfynd/A 35706-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -984,7 +984,7 @@
         <v>113324583</v>
       </c>
       <c r="B5" t="n">
-        <v>5165</v>
+        <v>5166</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,6 +1080,1651 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118102719</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78571</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>384302</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6721896</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118102724</v>
+      </c>
+      <c r="B7" t="n">
+        <v>86818</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>510</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>384159</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6721853</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118102730</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90448</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>112</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>384066</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6721601</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118102736</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78482</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Klingertjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>383795</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6721475</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118102721</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79523</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>384302</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6721898</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118102726</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78482</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>384058</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6721693</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118102731</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78516</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>185</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Klingertjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>384115</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6721593</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118102720</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79563</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>384298</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6721897</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118102725</v>
+      </c>
+      <c r="B14" t="n">
+        <v>86818</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>510</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>384062</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6721694</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118102729</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78218</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>384063</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6721643</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118102740</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79100</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Klingertjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>383638</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6721500</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>118102732</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90501</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Klingertjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>384101</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6721552</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>118102727</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80439</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>384067</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6721661</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>118102723</v>
+      </c>
+      <c r="B19" t="n">
+        <v>74578</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>384245</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6721783</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>118102728</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78219</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>384058</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6721639</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>118102735</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57288</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Klingertjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>383871</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6721459</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35706-2023 artfynd.xlsx
+++ b/artfynd/A 35706-2023 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118102719</v>
+        <v>118102728</v>
       </c>
       <c r="B6" t="n">
-        <v>78571</v>
+        <v>78219</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6450</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>384302</v>
+        <v>384058</v>
       </c>
       <c r="R6" t="n">
-        <v>6721896</v>
+        <v>6721639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118102724</v>
+        <v>118102721</v>
       </c>
       <c r="B7" t="n">
-        <v>86818</v>
+        <v>79523</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>384159</v>
+        <v>384302</v>
       </c>
       <c r="R7" t="n">
-        <v>6721853</v>
+        <v>6721898</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118102730</v>
+        <v>118102725</v>
       </c>
       <c r="B8" t="n">
-        <v>90448</v>
+        <v>86818</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>384066</v>
+        <v>384062</v>
       </c>
       <c r="R8" t="n">
-        <v>6721601</v>
+        <v>6721694</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118102736</v>
+        <v>118102719</v>
       </c>
       <c r="B9" t="n">
-        <v>78482</v>
+        <v>78571</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,41 +1401,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Klingertjärnen, Vrm</t>
+          <t>Hundsjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>383795</v>
+        <v>384302</v>
       </c>
       <c r="R9" t="n">
-        <v>6721475</v>
+        <v>6721896</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118102721</v>
+        <v>118102720</v>
       </c>
       <c r="B10" t="n">
-        <v>79523</v>
+        <v>79563</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>384302</v>
+        <v>384298</v>
       </c>
       <c r="R10" t="n">
-        <v>6721898</v>
+        <v>6721897</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118102726</v>
+        <v>118102724</v>
       </c>
       <c r="B11" t="n">
-        <v>78482</v>
+        <v>86818</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,13 +1633,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>384058</v>
+        <v>384159</v>
       </c>
       <c r="R11" t="n">
-        <v>6721693</v>
+        <v>6721853</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118102731</v>
+        <v>118102729</v>
       </c>
       <c r="B12" t="n">
-        <v>78516</v>
+        <v>78218</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,37 +1711,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Klingertjärnen, Vrm</t>
+          <t>Hundsjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>384115</v>
+        <v>384063</v>
       </c>
       <c r="R12" t="n">
-        <v>6721593</v>
+        <v>6721643</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118102720</v>
+        <v>118102731</v>
       </c>
       <c r="B13" t="n">
-        <v>79563</v>
+        <v>78516</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,34 +1813,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Vrm</t>
+          <t>Klingertjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>384298</v>
+        <v>384115</v>
       </c>
       <c r="R13" t="n">
-        <v>6721897</v>
+        <v>6721593</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118102725</v>
+        <v>118102732</v>
       </c>
       <c r="B14" t="n">
-        <v>86818</v>
+        <v>90501</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,34 +1915,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Vrm</t>
+          <t>Klingertjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>384062</v>
+        <v>384101</v>
       </c>
       <c r="R14" t="n">
-        <v>6721694</v>
+        <v>6721552</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118102729</v>
+        <v>118102736</v>
       </c>
       <c r="B15" t="n">
-        <v>78218</v>
+        <v>78482</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,37 +2017,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Vrm</t>
+          <t>Klingertjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>384063</v>
+        <v>383795</v>
       </c>
       <c r="R15" t="n">
-        <v>6721643</v>
+        <v>6721475</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118102732</v>
+        <v>118102727</v>
       </c>
       <c r="B17" t="n">
-        <v>90501</v>
+        <v>80439</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,34 +2221,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Klingertjärnen, Vrm</t>
+          <t>Hundsjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>384101</v>
+        <v>384067</v>
       </c>
       <c r="R17" t="n">
-        <v>6721552</v>
+        <v>6721661</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118102727</v>
+        <v>118102735</v>
       </c>
       <c r="B18" t="n">
-        <v>80439</v>
+        <v>57288</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,37 +2323,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Vrm</t>
+          <t>Klingertjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>384067</v>
+        <v>383871</v>
       </c>
       <c r="R18" t="n">
-        <v>6721661</v>
+        <v>6721459</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2383,6 +2391,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2511,10 +2524,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118102728</v>
+        <v>118102730</v>
       </c>
       <c r="B20" t="n">
-        <v>78219</v>
+        <v>90448</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2540,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>112</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,13 +2564,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>384058</v>
+        <v>384066</v>
       </c>
       <c r="R20" t="n">
-        <v>6721639</v>
+        <v>6721601</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2613,10 +2626,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118102735</v>
+        <v>118102726</v>
       </c>
       <c r="B21" t="n">
-        <v>57288</v>
+        <v>78482</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,45 +2642,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Klingertjärnen, Vrm</t>
+          <t>Hundsjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>383871</v>
+        <v>384058</v>
       </c>
       <c r="R21" t="n">
-        <v>6721459</v>
+        <v>6721693</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2697,11 +2702,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 35706-2023 artfynd.xlsx
+++ b/artfynd/A 35706-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2726,6 +2726,4800 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>118995686</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79111</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>384110</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6721690</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>118995728</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90478</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>383987</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6721558</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>118996307</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78582</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>383871</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6721448</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>118996309</v>
+      </c>
+      <c r="B25" t="n">
+        <v>5166</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>384053</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6721553</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>118995727</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78230</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>384056</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6721648</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>118995746</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78493</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>383780</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6721455</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>118996317</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78527</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>185</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>383837</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6721451</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>118995731</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78582</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>383850</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6721463</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>118995726</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79574</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>384062</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6721596</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>118995718</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78493</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>384164</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6721764</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>118995682</v>
+      </c>
+      <c r="B32" t="n">
+        <v>82272</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>383830</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6721423</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>118995724</v>
+      </c>
+      <c r="B33" t="n">
+        <v>95403</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>53</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>384083</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6721570</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>118995693</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78493</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>384205</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6721682</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>118995722</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78527</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>185</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>384086</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6721588</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>118995690</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78493</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>384120</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6721674</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>118996292</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5166</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>383814</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6721476</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>118995733</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78527</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>185</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>383827</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6721489</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>118995688</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78493</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>384112</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6721697</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>118995721</v>
+      </c>
+      <c r="B40" t="n">
+        <v>90478</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>384081</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6721589</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>118995681</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79111</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>383831</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6721450</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>118996304</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78230</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>384035</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6721562</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>118996310</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78527</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>185</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>383985</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6721537</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>118996303</v>
+      </c>
+      <c r="B44" t="n">
+        <v>5166</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>384092</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6721556</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>118995723</v>
+      </c>
+      <c r="B45" t="n">
+        <v>90478</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>384059</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6721657</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>118995729</v>
+      </c>
+      <c r="B46" t="n">
+        <v>90513</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>383982</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6721546</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>118995694</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78527</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>185</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>384220</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6721677</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>118996302</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78493</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>384064</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6721583</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>118996305</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91788</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>383827</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6721465</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>118995741</v>
+      </c>
+      <c r="B50" t="n">
+        <v>97772</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>383787</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6721448</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>118995720</v>
+      </c>
+      <c r="B51" t="n">
+        <v>90478</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>384171</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6721759</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>118995692</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78493</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>384260</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6721697</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>118995680</v>
+      </c>
+      <c r="B53" t="n">
+        <v>78493</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>383835</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6721497</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>118995730</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78493</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>384012</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6721532</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>118995717</v>
+      </c>
+      <c r="B55" t="n">
+        <v>78582</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>384231</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6721780</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>118995685</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78527</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>185</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>383828</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6721483</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>118995743</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78493</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>383778</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6721403</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>118995719</v>
+      </c>
+      <c r="B58" t="n">
+        <v>74597</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>308</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>384245</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6721780</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>118995736</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78493</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>383959</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6721510</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>118995725</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79609</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>384064</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6721594</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>118996295</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78493</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>384126</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6721667</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>118996308</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78493</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>384227</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6721691</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>118995687</v>
+      </c>
+      <c r="B63" t="n">
+        <v>90531</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>383933</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6721665</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>118995698</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78493</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>384398</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6721772</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>118995695</v>
+      </c>
+      <c r="B65" t="n">
+        <v>78493</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>384294</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6721702</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>118995735</v>
+      </c>
+      <c r="B66" t="n">
+        <v>80450</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>383854</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6721456</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>118996318</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78493</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>383951</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6721534</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>118995691</v>
+      </c>
+      <c r="B68" t="n">
+        <v>82272</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>384193</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6721676</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35706-2023 artfynd.xlsx
+++ b/artfynd/A 35706-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113324584</v>
+        <v>118995724</v>
       </c>
       <c r="B2" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Vrm</t>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384184</v>
+        <v>384083</v>
       </c>
       <c r="R2" t="n">
-        <v>6721712</v>
+        <v>6721570</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113324581</v>
+        <v>118102730</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>383924</v>
+        <v>384066</v>
       </c>
       <c r="R3" t="n">
-        <v>6721620</v>
+        <v>6721601</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113324582</v>
+        <v>118102731</v>
       </c>
       <c r="B4" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Vrm</t>
+          <t>Klingertjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384097</v>
+        <v>384115</v>
       </c>
       <c r="R4" t="n">
-        <v>6721549</v>
+        <v>6721593</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,62 +954,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113324583</v>
+        <v>118995685</v>
       </c>
       <c r="B5" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Vrm</t>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384140</v>
+        <v>383828</v>
       </c>
       <c r="R5" t="n">
-        <v>6721585</v>
+        <v>6721483</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118102724</v>
+        <v>118995694</v>
       </c>
       <c r="B6" t="n">
-        <v>86820</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,37 +1074,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Vrm</t>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>384159</v>
+        <v>384220</v>
       </c>
       <c r="R6" t="n">
-        <v>6721853</v>
+        <v>6721677</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,27 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118102730</v>
+        <v>118995722</v>
       </c>
       <c r="B7" t="n">
-        <v>90451</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,37 +1171,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Vrm</t>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>384066</v>
+        <v>384086</v>
       </c>
       <c r="R7" t="n">
-        <v>6721601</v>
+        <v>6721588</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,27 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118102725</v>
+        <v>118995733</v>
       </c>
       <c r="B8" t="n">
-        <v>86820</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Vrm</t>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>384062</v>
+        <v>383827</v>
       </c>
       <c r="R8" t="n">
-        <v>6721694</v>
+        <v>6721489</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,27 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118102728</v>
+        <v>118996310</v>
       </c>
       <c r="B9" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>384058</v>
+        <v>383985</v>
       </c>
       <c r="R9" t="n">
-        <v>6721639</v>
+        <v>6721537</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,49 +1439,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118102723</v>
+        <v>118996315</v>
       </c>
       <c r="B10" t="n">
-        <v>74580</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6439</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>384245</v>
+        <v>383702</v>
       </c>
       <c r="R10" t="n">
-        <v>6721783</v>
+        <v>6721482</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1581,27 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118102736</v>
+        <v>118996317</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,37 +1559,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Klingertjärnen, Vrm</t>
+          <t>Hundsjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>383795</v>
+        <v>383837</v>
       </c>
       <c r="R11" t="n">
-        <v>6721475</v>
+        <v>6721451</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1663,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1683,62 +1633,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118102721</v>
+        <v>118102737</v>
       </c>
       <c r="B12" t="n">
-        <v>79525</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Vrm</t>
+          <t>Klingertjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>384302</v>
+        <v>383800</v>
       </c>
       <c r="R12" t="n">
-        <v>6721898</v>
+        <v>6721507</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118102727</v>
+        <v>118995719</v>
       </c>
       <c r="B13" t="n">
-        <v>80441</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,34 +1753,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Vrm</t>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>384067</v>
+        <v>384245</v>
       </c>
       <c r="R13" t="n">
-        <v>6721661</v>
+        <v>6721780</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1887,27 +1827,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118102729</v>
+        <v>118102724</v>
       </c>
       <c r="B14" t="n">
-        <v>78220</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,13 +1874,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>384063</v>
+        <v>384159</v>
       </c>
       <c r="R14" t="n">
-        <v>6721643</v>
+        <v>6721853</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2001,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118102726</v>
+        <v>118102725</v>
       </c>
       <c r="B15" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>384058</v>
+        <v>384062</v>
       </c>
       <c r="R15" t="n">
-        <v>6721693</v>
+        <v>6721694</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118102732</v>
+        <v>118102727</v>
       </c>
       <c r="B16" t="n">
-        <v>90504</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,34 +2044,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Klingertjärnen, Vrm</t>
+          <t>Hundsjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>384101</v>
+        <v>384067</v>
       </c>
       <c r="R16" t="n">
-        <v>6721552</v>
+        <v>6721661</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,15 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118102731</v>
+        <v>118995735</v>
       </c>
       <c r="B17" t="n">
-        <v>78518</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,34 +2141,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Klingertjärnen, Vrm</t>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>384115</v>
+        <v>383854</v>
       </c>
       <c r="R17" t="n">
-        <v>6721593</v>
+        <v>6721456</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2275,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2295,27 +2215,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118102740</v>
+        <v>118995740</v>
       </c>
       <c r="B18" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,37 +2238,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Klingertjärnen, Vrm</t>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>383638</v>
+        <v>383669</v>
       </c>
       <c r="R18" t="n">
-        <v>6721500</v>
+        <v>6721515</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2377,12 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2397,27 +2312,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118102735</v>
+        <v>118102732</v>
       </c>
       <c r="B19" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,45 +2335,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Klingertjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>383871</v>
+        <v>384101</v>
       </c>
       <c r="R19" t="n">
-        <v>6721459</v>
+        <v>6721552</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2493,11 +2395,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2524,15 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118102720</v>
+        <v>118995729</v>
       </c>
       <c r="B20" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2540,34 +2432,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Vrm</t>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>384298</v>
+        <v>383982</v>
       </c>
       <c r="R20" t="n">
-        <v>6721897</v>
+        <v>6721546</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2594,12 +2486,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2614,62 +2506,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118102719</v>
+        <v>118995682</v>
       </c>
       <c r="B21" t="n">
-        <v>78573</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Vrm</t>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>384302</v>
+        <v>383830</v>
       </c>
       <c r="R21" t="n">
-        <v>6721896</v>
+        <v>6721423</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2696,12 +2583,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2716,62 +2603,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118996305</v>
+        <v>118995691</v>
       </c>
       <c r="B22" t="n">
-        <v>91809</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Vrm</t>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>383827</v>
+        <v>384193</v>
       </c>
       <c r="R22" t="n">
-        <v>6721465</v>
+        <v>6721676</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2818,62 +2700,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118995721</v>
+        <v>118996305</v>
       </c>
       <c r="B23" t="n">
-        <v>90496</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Uggenäs, Vrm</t>
+          <t>Hundsjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>384081</v>
+        <v>383827</v>
       </c>
       <c r="R23" t="n">
-        <v>6721589</v>
+        <v>6721465</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2920,62 +2797,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118995735</v>
+        <v>113324584</v>
       </c>
       <c r="B24" t="n">
-        <v>80468</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1049</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Uggenäs, Vrm</t>
+          <t>Hundsjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>383854</v>
+        <v>384184</v>
       </c>
       <c r="R24" t="n">
-        <v>6721456</v>
+        <v>6721712</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3002,12 +2874,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3022,49 +2894,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118995729</v>
+        <v>118995720</v>
       </c>
       <c r="B25" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3074,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>383982</v>
+        <v>384171</v>
       </c>
       <c r="R25" t="n">
-        <v>6721546</v>
+        <v>6721759</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3136,37 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118995727</v>
+        <v>118995721</v>
       </c>
       <c r="B26" t="n">
-        <v>78248</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3176,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>384056</v>
+        <v>384081</v>
       </c>
       <c r="R26" t="n">
-        <v>6721648</v>
+        <v>6721589</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3238,37 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118995690</v>
+        <v>118995723</v>
       </c>
       <c r="B27" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3278,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>384120</v>
+        <v>384059</v>
       </c>
       <c r="R27" t="n">
-        <v>6721674</v>
+        <v>6721657</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3340,37 +3197,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118995688</v>
+        <v>118995728</v>
       </c>
       <c r="B28" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3380,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>384112</v>
+        <v>383987</v>
       </c>
       <c r="R28" t="n">
-        <v>6721697</v>
+        <v>6721558</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3442,19 +3294,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118995746</v>
+        <v>113324581</v>
       </c>
       <c r="B29" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3478,14 +3325,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Uggenäs, Vrm</t>
+          <t>Hundsjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>383780</v>
+        <v>383924</v>
       </c>
       <c r="R29" t="n">
-        <v>6721455</v>
+        <v>6721620</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3512,12 +3359,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3532,31 +3379,26 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118996308</v>
+        <v>118102726</v>
       </c>
       <c r="B30" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3584,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>384227</v>
+        <v>384058</v>
       </c>
       <c r="R30" t="n">
-        <v>6721691</v>
+        <v>6721693</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3614,12 +3456,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3634,65 +3476,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118995717</v>
+        <v>118102736</v>
       </c>
       <c r="B31" t="n">
-        <v>78600</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Uggenäs, Vrm</t>
+          <t>Klingertjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>384231</v>
+        <v>383795</v>
       </c>
       <c r="R31" t="n">
-        <v>6721780</v>
+        <v>6721475</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3716,12 +3553,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3736,49 +3573,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118995694</v>
+        <v>118995680</v>
       </c>
       <c r="B32" t="n">
-        <v>78545</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3788,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>384220</v>
+        <v>383835</v>
       </c>
       <c r="R32" t="n">
-        <v>6721677</v>
+        <v>6721497</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3850,37 +3682,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118995719</v>
+        <v>118995688</v>
       </c>
       <c r="B33" t="n">
-        <v>74615</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3890,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>384245</v>
+        <v>384112</v>
       </c>
       <c r="R33" t="n">
-        <v>6721780</v>
+        <v>6721697</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3952,37 +3779,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118995741</v>
+        <v>118995690</v>
       </c>
       <c r="B34" t="n">
-        <v>97793</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3992,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>383787</v>
+        <v>384120</v>
       </c>
       <c r="R34" t="n">
-        <v>6721448</v>
+        <v>6721674</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4054,19 +3876,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118995680</v>
+        <v>118995692</v>
       </c>
       <c r="B35" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4094,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>383835</v>
+        <v>384260</v>
       </c>
       <c r="R35" t="n">
-        <v>6721497</v>
+        <v>6721697</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4156,50 +3973,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118996310</v>
+        <v>118995693</v>
       </c>
       <c r="B36" t="n">
-        <v>78545</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Vrm</t>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>383985</v>
+        <v>384205</v>
       </c>
       <c r="R36" t="n">
-        <v>6721537</v>
+        <v>6721682</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4246,49 +4058,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118995686</v>
+        <v>118995695</v>
       </c>
       <c r="B37" t="n">
-        <v>79129</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4298,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>384110</v>
+        <v>384294</v>
       </c>
       <c r="R37" t="n">
-        <v>6721690</v>
+        <v>6721702</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4360,37 +4167,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118995685</v>
+        <v>118995698</v>
       </c>
       <c r="B38" t="n">
-        <v>78545</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4400,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>383828</v>
+        <v>384398</v>
       </c>
       <c r="R38" t="n">
-        <v>6721483</v>
+        <v>6721772</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4462,50 +4264,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118996317</v>
+        <v>118995718</v>
       </c>
       <c r="B39" t="n">
-        <v>78545</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Vrm</t>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>383837</v>
+        <v>384164</v>
       </c>
       <c r="R39" t="n">
-        <v>6721451</v>
+        <v>6721764</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4552,49 +4349,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118995722</v>
+        <v>118995730</v>
       </c>
       <c r="B40" t="n">
-        <v>78545</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4604,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>384086</v>
+        <v>384012</v>
       </c>
       <c r="R40" t="n">
-        <v>6721588</v>
+        <v>6721532</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4666,19 +4458,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118995736</v>
+        <v>118995734</v>
       </c>
       <c r="B41" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4706,10 +4493,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>383959</v>
+        <v>383768</v>
       </c>
       <c r="R41" t="n">
-        <v>6721510</v>
+        <v>6721490</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4768,37 +4555,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118995681</v>
+        <v>118995736</v>
       </c>
       <c r="B42" t="n">
-        <v>79129</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4808,10 +4590,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>383831</v>
+        <v>383959</v>
       </c>
       <c r="R42" t="n">
-        <v>6721450</v>
+        <v>6721510</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4870,19 +4652,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118995718</v>
+        <v>118995739</v>
       </c>
       <c r="B43" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4910,10 +4687,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>384164</v>
+        <v>383644</v>
       </c>
       <c r="R43" t="n">
-        <v>6721764</v>
+        <v>6721547</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4972,19 +4749,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118996295</v>
+        <v>118995743</v>
       </c>
       <c r="B44" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5008,14 +4780,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Vrm</t>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>384126</v>
+        <v>383778</v>
       </c>
       <c r="R44" t="n">
-        <v>6721667</v>
+        <v>6721403</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5062,31 +4834,26 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118995730</v>
+        <v>118995744</v>
       </c>
       <c r="B45" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5114,10 +4881,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>384012</v>
+        <v>383718</v>
       </c>
       <c r="R45" t="n">
-        <v>6721532</v>
+        <v>6721481</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5176,19 +4943,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118996302</v>
+        <v>118995746</v>
       </c>
       <c r="B46" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5212,14 +4974,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Vrm</t>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>384064</v>
+        <v>383780</v>
       </c>
       <c r="R46" t="n">
-        <v>6721583</v>
+        <v>6721455</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5266,49 +5028,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118995682</v>
+        <v>118995747</v>
       </c>
       <c r="B47" t="n">
-        <v>82290</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5318,10 +5075,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>383830</v>
+        <v>383683</v>
       </c>
       <c r="R47" t="n">
-        <v>6721423</v>
+        <v>6721510</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5380,50 +5137,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118995724</v>
+        <v>118996295</v>
       </c>
       <c r="B48" t="n">
-        <v>95424</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Uggenäs, Vrm</t>
+          <t>Hundsjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>384083</v>
+        <v>384126</v>
       </c>
       <c r="R48" t="n">
-        <v>6721570</v>
+        <v>6721667</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5470,62 +5222,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118995691</v>
+        <v>118996296</v>
       </c>
       <c r="B49" t="n">
-        <v>82290</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Uggenäs, Vrm</t>
+          <t>Hundsjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>384193</v>
+        <v>383697</v>
       </c>
       <c r="R49" t="n">
-        <v>6721676</v>
+        <v>6721489</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5572,49 +5319,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118996304</v>
+        <v>118996297</v>
       </c>
       <c r="B50" t="n">
-        <v>78248</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5624,10 +5366,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>384035</v>
+        <v>383780</v>
       </c>
       <c r="R50" t="n">
-        <v>6721562</v>
+        <v>6721497</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5686,50 +5428,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118995728</v>
+        <v>118996299</v>
       </c>
       <c r="B51" t="n">
-        <v>90496</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Uggenäs, Vrm</t>
+          <t>Hundsjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>383987</v>
+        <v>383679</v>
       </c>
       <c r="R51" t="n">
-        <v>6721558</v>
+        <v>6721518</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5776,62 +5513,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118995720</v>
+        <v>118996302</v>
       </c>
       <c r="B52" t="n">
-        <v>90496</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Uggenäs, Vrm</t>
+          <t>Hundsjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>384171</v>
+        <v>384064</v>
       </c>
       <c r="R52" t="n">
-        <v>6721759</v>
+        <v>6721583</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5878,49 +5610,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118996292</v>
+        <v>118996306</v>
       </c>
       <c r="B53" t="n">
-        <v>5167</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5930,10 +5657,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>383814</v>
+        <v>384380</v>
       </c>
       <c r="R53" t="n">
-        <v>6721476</v>
+        <v>6721910</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5992,50 +5719,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118995687</v>
+        <v>118996308</v>
       </c>
       <c r="B54" t="n">
-        <v>90549</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Uggenäs, Vrm</t>
+          <t>Hundsjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>383933</v>
+        <v>384227</v>
       </c>
       <c r="R54" t="n">
-        <v>6721665</v>
+        <v>6721691</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6082,31 +5804,26 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118995743</v>
+        <v>118996314</v>
       </c>
       <c r="B55" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -6130,14 +5847,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Uggenäs, Vrm</t>
+          <t>Hundsjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>383778</v>
+        <v>384382</v>
       </c>
       <c r="R55" t="n">
-        <v>6721403</v>
+        <v>6721942</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6184,31 +5901,26 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118995695</v>
+        <v>118996316</v>
       </c>
       <c r="B56" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6232,14 +5944,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Uggenäs, Vrm</t>
+          <t>Hundsjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>384294</v>
+        <v>383702</v>
       </c>
       <c r="R56" t="n">
-        <v>6721702</v>
+        <v>6721482</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6286,12 +5998,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6301,16 +6013,11 @@
         <v>118996318</v>
       </c>
       <c r="B57" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -6400,37 +6107,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118996307</v>
+        <v>118996319</v>
       </c>
       <c r="B58" t="n">
-        <v>78600</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6440,10 +6142,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>383871</v>
+        <v>383649</v>
       </c>
       <c r="R58" t="n">
-        <v>6721448</v>
+        <v>6721534</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6502,15 +6204,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118995725</v>
+        <v>118102723</v>
       </c>
       <c r="B59" t="n">
-        <v>79627</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6518,34 +6215,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6463</v>
+        <v>6439</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Uggenäs, Vrm</t>
+          <t>Hundsjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>384064</v>
+        <v>384245</v>
       </c>
       <c r="R59" t="n">
-        <v>6721594</v>
+        <v>6721783</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6572,12 +6269,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6592,27 +6289,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118995726</v>
+        <v>118102729</v>
       </c>
       <c r="B60" t="n">
-        <v>79592</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6620,37 +6312,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Uggenäs, Vrm</t>
+          <t>Hundsjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>384062</v>
+        <v>384063</v>
       </c>
       <c r="R60" t="n">
-        <v>6721596</v>
+        <v>6721643</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6674,12 +6366,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6694,49 +6386,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118996309</v>
+        <v>118102719</v>
       </c>
       <c r="B61" t="n">
-        <v>5167</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100526</v>
+        <v>6450</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6746,10 +6433,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>384053</v>
+        <v>384302</v>
       </c>
       <c r="R61" t="n">
-        <v>6721553</v>
+        <v>6721896</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6776,12 +6463,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6796,62 +6483,57 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118996303</v>
+        <v>118995717</v>
       </c>
       <c r="B62" t="n">
-        <v>5167</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>6450</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Vrm</t>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>384092</v>
+        <v>384231</v>
       </c>
       <c r="R62" t="n">
-        <v>6721556</v>
+        <v>6721780</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6898,27 +6580,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118995693</v>
+        <v>118995731</v>
       </c>
       <c r="B63" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6926,21 +6603,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6950,10 +6627,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>384205</v>
+        <v>383850</v>
       </c>
       <c r="R63" t="n">
-        <v>6721682</v>
+        <v>6721463</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7012,15 +6689,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118995692</v>
+        <v>118996307</v>
       </c>
       <c r="B64" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7028,34 +6700,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Uggenäs, Vrm</t>
+          <t>Hundsjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>384260</v>
+        <v>383871</v>
       </c>
       <c r="R64" t="n">
-        <v>6721697</v>
+        <v>6721448</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7102,27 +6774,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118995698</v>
+        <v>118102740</v>
       </c>
       <c r="B65" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7130,37 +6797,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Uggenäs, Vrm</t>
+          <t>Klingertjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>384398</v>
+        <v>383638</v>
       </c>
       <c r="R65" t="n">
-        <v>6721772</v>
+        <v>6721500</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7184,12 +6851,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7204,49 +6871,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118995723</v>
+        <v>118995681</v>
       </c>
       <c r="B66" t="n">
-        <v>90496</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7256,10 +6918,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>384059</v>
+        <v>383831</v>
       </c>
       <c r="R66" t="n">
-        <v>6721657</v>
+        <v>6721450</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7318,37 +6980,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118995731</v>
+        <v>118995686</v>
       </c>
       <c r="B67" t="n">
-        <v>78600</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7358,10 +7015,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>383850</v>
+        <v>384110</v>
       </c>
       <c r="R67" t="n">
-        <v>6721463</v>
+        <v>6721690</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7420,15 +7077,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118995733</v>
+        <v>113324582</v>
       </c>
       <c r="B68" t="n">
-        <v>78545</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7436,34 +7088,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Hundsjöberget, Uggenäs, Vrm</t>
+          <t>Hundsjöberget, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>383827</v>
+        <v>384097</v>
       </c>
       <c r="R68" t="n">
-        <v>6721489</v>
+        <v>6721549</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7490,12 +7142,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7510,15 +7162,1289 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>118102720</v>
+      </c>
+      <c r="B69" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>384298</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6721897</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>118995726</v>
+      </c>
+      <c r="B70" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>384062</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6721596</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
           <t>Helena Malmestrand</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
+      <c r="AX70" t="inlineStr">
         <is>
           <t>Helena Malmestrand</t>
         </is>
       </c>
-      <c r="AY68" t="inlineStr"/>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>118995725</v>
+      </c>
+      <c r="B71" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>384064</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6721594</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>118102735</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Klingertjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>383871</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6721459</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>113324583</v>
+      </c>
+      <c r="B73" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>384140</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6721585</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>118996292</v>
+      </c>
+      <c r="B74" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>383814</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6721476</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>118996303</v>
+      </c>
+      <c r="B75" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>384092</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6721556</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>118996309</v>
+      </c>
+      <c r="B76" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>384053</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6721553</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>118995741</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>383787</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6721448</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>118102728</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>384058</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6721639</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>118995727</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Uggenäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>384056</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6721648</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>118996304</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>384035</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6721562</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>118102721</v>
+      </c>
+      <c r="B81" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Hundsjöberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>384302</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6721898</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35706-2023 artfynd.xlsx
+++ b/artfynd/A 35706-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY81"/>
+  <dimension ref="A1:AZ81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995724</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118102730</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118102731</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995685</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995694</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995722</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995733</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118996310</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118996315</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118996317</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118102737</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995719</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118102724</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118102725</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118102727</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995735</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995740</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118102732</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995729</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995682</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995691</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118996305</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113324584</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995720</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995721</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995723</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995728</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113324581</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118102726</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118102736</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995680</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995688</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995690</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995692</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995693</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,6 +4344,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995695</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4261,6 +4446,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995698</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4358,6 +4548,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995718</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4455,6 +4650,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995730</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4552,6 +4752,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995734</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4649,6 +4854,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995736</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4746,6 +4956,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995739</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4843,6 +5058,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995743</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4940,6 +5160,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995744</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5037,6 +5262,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995746</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5134,6 +5364,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995747</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5231,6 +5466,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118996295</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5328,6 +5568,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118996296</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5425,6 +5670,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118996297</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5522,6 +5772,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118996299</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5619,6 +5874,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118996302</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5716,6 +5976,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118996306</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5813,6 +6078,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118996308</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5910,6 +6180,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118996314</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6007,6 +6282,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118996316</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6104,6 +6384,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118996318</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6201,6 +6486,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118996319</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6298,6 +6588,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118102723</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6395,6 +6690,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118102729</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6492,6 +6792,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118102719</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6589,6 +6894,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995717</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6686,6 +6996,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995731</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6783,6 +7098,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118996307</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6880,6 +7200,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118102740</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6977,6 +7302,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995681</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7074,6 +7404,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995686</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7171,6 +7506,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113324582</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7268,6 +7608,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118102720</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7365,6 +7710,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995726</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7462,6 +7812,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995725</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7572,6 +7927,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118102735</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7669,6 +8029,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113324583</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7766,6 +8131,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118996292</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7863,6 +8233,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118996303</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7960,6 +8335,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118996309</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8057,6 +8437,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995741</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8154,6 +8539,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118102728</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8251,6 +8641,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995727</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8348,6 +8743,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118996304</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8445,8 +8845,95 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118102721</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>